--- a/i18n/tr.xlsx
+++ b/i18n/tr.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -3435,144 +3435,9 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Birds Cards in Hand</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>No Goal</t>
-  </si>
-  <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
-  </si>
-  <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
-    <t>In Forest</t>
-  </si>
-  <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>Translated</t>
   </si>
   <si>
@@ -3622,6 +3487,141 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
 </sst>
 </file>
@@ -3631,7 +3631,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;PRAWDA&quot;;&quot;PRAWDA&quot;;&quot;FAŁSZ&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3643,7 +3643,8 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3662,7 +3663,15 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3686,7 +3695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -3713,6 +3722,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Excel Built-in Normal" xfId="1"/>
@@ -3943,7 +3953,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>1195</v>
+        <v>1150</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -4784,7 +4794,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>1188</v>
+        <v>1143</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -6559,7 +6569,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1189</v>
+        <v>1144</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>298</v>
@@ -7347,7 +7357,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1191</v>
+        <v>1146</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>375</v>
@@ -8305,7 +8315,7 @@
         <v>479</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1192</v>
+        <v>1147</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>13</v>
@@ -11270,7 +11280,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="14" t="s">
-        <v>1194</v>
+        <v>1149</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>783</v>
@@ -11584,7 +11594,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>1190</v>
+        <v>1145</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>810</v>
@@ -13271,7 +13281,7 @@
         <v>984</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1193</v>
+        <v>1148</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>903</v>
@@ -14797,7 +14807,7 @@
         <v>2000</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1133</v>
+        <v>1151</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>13</v>
@@ -14811,7 +14821,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>1134</v>
+        <v>1152</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>13</v>
@@ -14825,7 +14835,7 @@
         <v>2002</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1135</v>
+        <v>1153</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>13</v>
@@ -14839,7 +14849,7 @@
         <v>2013</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1136</v>
+        <v>1154</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>13</v>
@@ -14853,7 +14863,7 @@
         <v>2014</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1137</v>
+        <v>1155</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>13</v>
@@ -14867,7 +14877,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1138</v>
+        <v>1156</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>13</v>
@@ -14881,7 +14891,7 @@
         <v>2010</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1139</v>
+        <v>1157</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>13</v>
@@ -14895,7 +14905,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>1140</v>
+        <v>1158</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>13</v>
@@ -14909,7 +14919,7 @@
         <v>2021</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1141</v>
+        <v>1159</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>13</v>
@@ -14923,7 +14933,7 @@
         <v>2022</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1142</v>
+        <v>1160</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>13</v>
@@ -14937,7 +14947,7 @@
         <v>2012</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1143</v>
+        <v>1161</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>13</v>
@@ -14951,7 +14961,7 @@
         <v>2011</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1144</v>
+        <v>1162</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>13</v>
@@ -14965,7 +14975,7 @@
         <v>2015</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1145</v>
+        <v>1163</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>13</v>
@@ -14979,7 +14989,7 @@
         <v>2016</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1146</v>
+        <v>1164</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>13</v>
@@ -14993,7 +15003,7 @@
         <v>2023</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1147</v>
+        <v>1165</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>13</v>
@@ -15007,7 +15017,7 @@
         <v>2024</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1148</v>
+        <v>1166</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>13</v>
@@ -15021,7 +15031,7 @@
         <v>2020</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1149</v>
+        <v>1167</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>64</v>
@@ -15035,7 +15045,7 @@
         <v>2003</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1150</v>
+        <v>1133</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>64</v>
@@ -15049,7 +15059,7 @@
         <v>2004</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1151</v>
+        <v>1168</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>64</v>
@@ -15063,7 +15073,7 @@
         <v>2006</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>64</v>
@@ -15077,7 +15087,7 @@
         <v>2005</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1153</v>
+        <v>1170</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>64</v>
@@ -15091,7 +15101,7 @@
         <v>2018</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1154</v>
+        <v>1171</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>64</v>
@@ -15105,7 +15115,7 @@
         <v>2009</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>64</v>
@@ -15119,7 +15129,7 @@
         <v>2025</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>64</v>
@@ -15133,7 +15143,7 @@
         <v>2007</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>64</v>
@@ -15147,7 +15157,7 @@
         <v>2019</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>64</v>
@@ -15161,7 +15171,7 @@
         <v>2031</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1159</v>
+        <v>1176</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>714</v>
@@ -15175,7 +15185,7 @@
         <v>2030</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1160</v>
+        <v>1177</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>714</v>
@@ -15189,7 +15199,7 @@
         <v>2033</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>714</v>
@@ -15203,7 +15213,7 @@
         <v>2032</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1162</v>
+        <v>1179</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>714</v>
@@ -15217,7 +15227,7 @@
         <v>2026</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1163</v>
+        <v>1180</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>714</v>
@@ -15231,7 +15241,7 @@
         <v>2027</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1164</v>
+        <v>1181</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>714</v>
@@ -15245,7 +15255,7 @@
         <v>2029</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1165</v>
+        <v>1182</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>714</v>
@@ -15259,7 +15269,7 @@
         <v>2028</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>1166</v>
+        <v>1183</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>714</v>
@@ -15272,8 +15282,8 @@
       <c r="A36" s="2">
         <v>2043</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>1167</v>
+      <c r="B36" s="16" t="s">
+        <v>1184</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>903</v>
@@ -15287,7 +15297,7 @@
         <v>2040</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>903</v>
@@ -15301,7 +15311,7 @@
         <v>2035</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>903</v>
@@ -15315,7 +15325,7 @@
         <v>2041</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>1170</v>
+        <v>1187</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>903</v>
@@ -15329,7 +15339,7 @@
         <v>2042</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>1171</v>
+        <v>1188</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>903</v>
@@ -15343,7 +15353,7 @@
         <v>2044</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1172</v>
+        <v>1189</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>903</v>
@@ -15357,7 +15367,7 @@
         <v>2036</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>903</v>
@@ -15371,7 +15381,7 @@
         <v>2034</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>1174</v>
+        <v>1191</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>903</v>
@@ -15385,7 +15395,7 @@
         <v>2037</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>1175</v>
+        <v>1192</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>903</v>
@@ -15399,7 +15409,7 @@
         <v>2038</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>1176</v>
+        <v>1193</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>903</v>
@@ -15413,7 +15423,7 @@
         <v>2039</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>1177</v>
+        <v>1194</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>903</v>
@@ -15427,7 +15437,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1178</v>
+        <v>1195</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>903</v>
@@ -15461,37 +15471,37 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1179</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1180</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1181</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1182</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1183</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1184</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1185</v>
+        <v>1140</v>
       </c>
     </row>
   </sheetData>
@@ -15517,12 +15527,12 @@
         <v>1081</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1186</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1187</v>
+        <v>1142</v>
       </c>
       <c r="B2" s="12" t="b">
         <f>FALSE()</f>
